--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -273,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA78" headerRowCount="1">
-  <autoFilter ref="A1:AA78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA79" headerRowCount="1">
+  <autoFilter ref="A1:AA79"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA78"/>
+  <dimension ref="A1:AA79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11236,6 +11236,143 @@
       <c r="AA78" s="7" t="inlineStr">
         <is>
           <t>#10</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="120" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>BUG-20260911-078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Data loss / availability</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Record the gap, never fill it</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Drop everything -- blocks merge</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>INF</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>CI's first step -- `python3 tests/selftest.py`, run before `pip install` because docs/03 promises the suite runs on the standard library alone -- died with `ModuleNotFoundError: No module named 'yaml'`, so EVERY later step was skipped and CI was red on every branch, main included, from 2026-09-09. 79 of 187 test functions transitively import PyYAML; the promise had been false since the metric engine landed</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>"Standard library only" was a property of the suite when it was written and was never enforced by anything. `test_metric_engine_contract` calls `metrics.load_intervals(config/intervals.yaml)`, which does `import yaml`, and 78 more tests reach PyYAML the same way -- through `load_intervals`, through `navanax.cli`, or by reading `config/assumptions.yaml` directly. Locally the suite passes because PyYAML is installed, so the divergence was invisible to every developer and visible only in the one environment that has no dependencies: CI's first step. A bare `ModuleNotFoundError` out of a test aborts the runner, so the failure was total rather than partial, and GitHub Actions skips every subsequent step of a failed job -- one missing module silenced eleven gates.</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>No data was lost or altered -- this is a loss of VERIFICATION, not of records. What was lost is every automated check for two days on every branch: the bug-ledger consistency gate, the secret scan (REQ-N-11), the transaction-capability check (REQ-N-14), the DataIntegrityError re-raise check, lint, and the only place python-zstandard's real multi-frame behaviour is ever exercised (BUG-20260909-010's whole point). Every merge in that window was made against a pipeline that had proven nothing. It is logged S2 because the thing that was lost was recoverable and is now recovered by re-running, not because anything in the landing zone or the bitemporal store moved.</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>A first-class skip. `needs("yaml")` is a decorator at the definition site (a list kept elsewhere is the drift BUG-20260909-038 removed) that records the modules a test cannot run without; `missing_modules` answers by actually importing, and `run_suite` records the test in SKIPPED -- printed by name at the point it would have run, listed by name above the summary, counted in its own column, never added to PASS. The summary line is now `187 test functions, 806 passed, 0 failed, 79 skipped (needs: yaml)` with the module named, and the exit code is 0 only when nothing FAILED. The guard that keeps that honest is `--no-skips`: it exits non-zero if anything was skipped at all. `tools/gates.py` runs the suite that way, so a developer on a machine with the dependencies can never see a skip and read it as fine, and a NEW CI step after `Install` runs it that way too, so the 79 tests are genuinely executed on every push and cannot quietly disappear. The stdlib-only step is unchanged and now passes with skips; no existing test was weakened, deleted, or had an assertion changed.</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Nothing watched CI's own colour. Every gate in this repo checks the code; none checked that the thing running the gates was still running. A red pipeline on main for two days generated no alert because the only consumer of that signal was a human opening the Actions tab. The narrower gap is that the stdlib-only claim was documentation, not a test: no run anywhere executed the suite with the dependencies actually absent, so the claim could decay silently for as long as it liked. The skip mechanism does not fix that by itself -- a skip is still a test that did not run -- which is why `--no-skips` exists in gates and in CI, and why the regression tests mutation-check both halves: making a skip count as a pass fails them, and making strict mode ignore skips fails them.</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>REQ-N-16</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py:L58  ·  tests/selftest.py:L1825  ·  .github/workflows/ci.yml:L24  ·  tools/gates.py:L117</t>
+        </is>
+      </c>
+      <c r="T79" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/spencerwon/navanax1/blob/tester/tests/selftest.py#L58 https://github.com/spencerwon/navanax1/blob/tester/tests/selftest.py#L1825 https://github.com/spencerwon/navanax1/blob/tester/.github/workflows/ci.yml#L24 https://github.com/spencerwon/navanax1/blob/tester/tools/gates.py#L117</t>
+        </is>
+      </c>
+      <c r="U79" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py::test_runner_records_a_skip_as_skipped_and_never_as_a_pass tests/selftest.py::test_no_skips_mode_refuses_to_exit_zero_when_anything_was_skipped tests/selftest.py::test_a_declared_module_that_is_present_does_not_skip_the_test</t>
+        </is>
+      </c>
+      <c r="V79" s="3" t="inlineStr">
+        <is>
+          <t>platform-engineer, reading the GitHub Actions log</t>
+        </is>
+      </c>
+      <c r="W79" s="3" t="inlineStr">
+        <is>
+          <t>ci</t>
+        </is>
+      </c>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09T00:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="Y79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11T16:10:00-05:00</t>
+        </is>
+      </c>
+      <c r="Z79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11T17:05:00-05:00</t>
+        </is>
+      </c>
+      <c r="AA79" s="7" t="inlineStr">
+        <is>
+          <t>#11</t>
         </is>
       </c>
     </row>
@@ -11386,10 +11523,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA77" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T78" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA78" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T79" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA79" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId146"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId148"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11468,11 +11607,11 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$78,$A5,'Bug log'!$K$2:$K$78,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A5,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$78,$A5)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$79,$A5)</f>
         <v/>
       </c>
     </row>
@@ -11493,11 +11632,11 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$78,$A6,'Bug log'!$K$2:$K$78,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A6,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$78,$A6)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$79,$A6)</f>
         <v/>
       </c>
     </row>
@@ -11518,11 +11657,11 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$78,$A7,'Bug log'!$K$2:$K$78,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A7,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$78,$A7)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$79,$A7)</f>
         <v/>
       </c>
     </row>
@@ -11543,11 +11682,11 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$78,$A8,'Bug log'!$K$2:$K$78,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A8,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$78,$A8)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$79,$A8)</f>
         <v/>
       </c>
     </row>
@@ -11568,11 +11707,11 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$78,$A9,'Bug log'!$K$2:$K$78,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A9,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$78,$A9)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$79,$A9)</f>
         <v/>
       </c>
     </row>
@@ -11593,11 +11732,11 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$78,$A10,'Bug log'!$K$2:$K$78,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A10,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$78,$A10)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$79,$A10)</f>
         <v/>
       </c>
     </row>

--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -11297,12 +11297,12 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>CI's first step -- `python3 tests/selftest.py`, run before `pip install` because docs/03 promises the suite runs on the standard library alone -- died with `ModuleNotFoundError: No module named 'yaml'`, so EVERY later step was skipped and CI was red on every branch, main included, from 2026-09-09. 79 of 187 test functions transitively import PyYAML; the promise had been false since the metric engine landed</t>
+          <t>CI's first step -- `python3 tests/selftest.py`, run before `pip install` because docs/03 promises the suite runs on the standard library alone -- died with `ModuleNotFoundError: No module named 'yaml'`, so EVERY later step was skipped and CI was red on every branch, main included, from 2026-09-09. 81 of 187 test functions need PyYAML: 79 import it in-process, and 2 SPAWN `python -m navanax.cli`, whose CHILD dies at cli.py:40. The first fix shipped still-red because it was verified with an in-process import blocker, which a child process does not inherit</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>"Standard library only" was a property of the suite when it was written and was never enforced by anything. `test_metric_engine_contract` calls `metrics.load_intervals(config/intervals.yaml)`, which does `import yaml`, and 78 more tests reach PyYAML the same way -- through `load_intervals`, through `navanax.cli`, or by reading `config/assumptions.yaml` directly. Locally the suite passes because PyYAML is installed, so the divergence was invisible to every developer and visible only in the one environment that has no dependencies: CI's first step. A bare `ModuleNotFoundError` out of a test aborts the runner, so the failure was total rather than partial, and GitHub Actions skips every subsequent step of a failed job -- one missing module silenced eleven gates.</t>
+          <t>"Standard library only" was a property of the suite when it was written and was never enforced by anything. `test_metric_engine_contract` calls `metrics.load_intervals(config/intervals.yaml)`, which does `import yaml`, and 78 more tests reach PyYAML the same way -- through `load_intervals`, through `navanax.cli`, or by reading `config/assumptions.yaml` directly. Locally the suite passes because PyYAML is installed, so the divergence was invisible to every developer and visible only in the one environment that has no dependencies: CI's first step. A bare `ModuleNotFoundError` out of a test aborts the runner, so the failure was total rather than partial, and GitHub Actions skips every subsequent step of a failed job -- one missing module silenced eleven gates. THE SECOND ROOT CAUSE, and the more expensive one: the first fix was verified by making `yaml` unimportable with an in-process `sys.meta_path` finder. A CHILD PROCESS DOES NOT INHERIT THAT. `test_ingest_supervised_exit_code_contract` and `test_ingest_supervised_sigterm_is_a_clean_stop` spawn `python -m navanax.cli ingest --supervised`, and that child imported the real PyYAML out of the developer's environment, so both tests passed under the blocker and were never declared. In CI, where there is no PyYAML anywhere, the child dies at `src/navanax/cli.py:40` and the PARENT reports an ordinary failed check -- `ingest --supervised: SIGTERM exits 0 ... exit=1` -- with the ModuleNotFoundError buried in a captured traceback and nothing in the summary naming a missing module. So the fix shipped, CI stayed red, and the second failure looked nothing like the first. An in-process import blocker is NOT a valid check of the stdlib-only floor and must never be used as one again; the only valid check is a bare interpreter, which is what CI has.</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -11312,12 +11312,12 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>A first-class skip. `needs("yaml")` is a decorator at the definition site (a list kept elsewhere is the drift BUG-20260909-038 removed) that records the modules a test cannot run without; `missing_modules` answers by actually importing, and `run_suite` records the test in SKIPPED -- printed by name at the point it would have run, listed by name above the summary, counted in its own column, never added to PASS. The summary line is now `187 test functions, 806 passed, 0 failed, 79 skipped (needs: yaml)` with the module named, and the exit code is 0 only when nothing FAILED. The guard that keeps that honest is `--no-skips`: it exits non-zero if anything was skipped at all. `tools/gates.py` runs the suite that way, so a developer on a machine with the dependencies can never see a skip and read it as fine, and a NEW CI step after `Install` runs it that way too, so the 79 tests are genuinely executed on every push and cannot quietly disappear. The stdlib-only step is unchanged and now passes with skips; no existing test was weakened, deleted, or had an assertion changed.</t>
+          <t>A first-class skip. `needs("yaml")` is a decorator at the definition site (a list kept elsewhere is the drift BUG-20260909-038 removed) that records the modules a test cannot run without; `missing_modules` answers by actually importing, and `run_suite` records the test in SKIPPED -- printed by name at the point it would have run, listed by name above the summary, counted in its own column, never added to PASS. The summary line is now `191 test functions, 829 passed, 0 failed, 81 skipped (needs: yaml)` with the module named, and the exit code is 0 only when nothing FAILED. The guard that keeps that honest is `--no-skips`: it exits non-zero if anything was skipped at all. `tools/gates.py` runs the suite that way, so a developer on a machine with the dependencies can never see a skip and read it as fine, and a NEW CI step after `Install` runs it that way too, so the 79 tests are genuinely executed on every push and cannot quietly disappear. The stdlib-only step is unchanged and now passes with skips; no existing test was weakened, deleted, or had an assertion changed. Verification is now specified rather than improvised. `rm -rf /tmp/bare &amp;&amp; python3 -m venv /tmp/bare`, then `/tmp/bare/bin/python tests/selftest.py` (must exit 0, 0 failed) and the same with `--no-skips` (must exit non-zero), is the ONLY accepted check: a child spawned with `sys.executable` inherits that interpreter, so the subprocess class is covered. One hole the bare venv does not close by itself is recorded in docs/03 §4.6.1 -- tests that run a `*.command` shell script spawn `bash`, and every one of those scripts picks its interpreter by searching PATH (`for c in python3.14 ... python3`) instead of using `sys.executable`, so on a developer machine that search finds the system PyYAML. Re-running behind a PATH of wrappers pointing at the bare interpreter closes it; as of 2026-09-14 that changes nothing -- the same failures and no others -- but a new script-spawning test could change that silently.</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>Nothing watched CI's own colour. Every gate in this repo checks the code; none checked that the thing running the gates was still running. A red pipeline on main for two days generated no alert because the only consumer of that signal was a human opening the Actions tab. The narrower gap is that the stdlib-only claim was documentation, not a test: no run anywhere executed the suite with the dependencies actually absent, so the claim could decay silently for as long as it liked. The skip mechanism does not fix that by itself -- a skip is still a test that did not run -- which is why `--no-skips` exists in gates and in CI, and why the regression tests mutation-check both halves: making a skip count as a pass fails them, and making strict mode ignore skips fails them.</t>
+          <t>Nothing watched CI's own colour. Every gate in this repo checks the code; none checked that the thing running the gates was still running. A red pipeline on main for two days generated no alert because the only consumer of that signal was a human opening the Actions tab. The narrower gap is that the stdlib-only claim was documentation, not a test: no run anywhere executed the suite with the dependencies actually absent, so the claim could decay silently for as long as it liked. The skip mechanism does not fix that by itself -- a skip is still a test that did not run -- which is why `--no-skips` exists in gates and in CI, and why the regression tests mutation-check both halves: making a skip count as a pass fails them, and making strict mode ignore skips fails them. The gap that let it ship red a SECOND time is a gap in how the first fix was CHECKED, not in the fix itself. The blocker was in-process, the masked tests were the ones that fork, and nothing in the suite or the docs said which verification method was valid -- so a reasonable method that happened to be wrong was used and its clean result was believed. docs/03 §4.6.1 now names the bare venv as the only accepted check and says in as many words that an in-process blocker is not one. `test_every_test_that_spawns_navanax_cli_declares_that_it_needs_yaml` is the tripwire between bare-venv runs: it walks the argv of every `subprocess.run`/`Popen` in the suite and fails if a test that spawns `navanax.cli` is missing its declaration. It scans source rather than running, because proving this dynamically needs an interpreter with no PyYAML -- which is exactly what the machine running the gate does not have.</t>
         </is>
       </c>
       <c r="Q79" s="6" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="U79" s="6" t="inlineStr">
         <is>
-          <t>tests/selftest.py::test_runner_records_a_skip_as_skipped_and_never_as_a_pass tests/selftest.py::test_no_skips_mode_refuses_to_exit_zero_when_anything_was_skipped tests/selftest.py::test_a_declared_module_that_is_present_does_not_skip_the_test</t>
+          <t>tests/selftest.py::test_runner_records_a_skip_as_skipped_and_never_as_a_pass tests/selftest.py::test_no_skips_mode_refuses_to_exit_zero_when_anything_was_skipped tests/selftest.py::test_a_declared_module_that_is_present_does_not_skip_the_test tests/selftest.py::test_every_test_that_spawns_navanax_cli_declares_that_it_needs_yaml</t>
         </is>
       </c>
       <c r="V79" s="3" t="inlineStr">

--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -273,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA79" headerRowCount="1">
-  <autoFilter ref="A1:AA79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA80" headerRowCount="1">
+  <autoFilter ref="A1:AA80"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA79"/>
+  <dimension ref="A1:AA80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11375,6 +11375,135 @@
           <t>#11</t>
         </is>
       </c>
+    </row>
+    <row r="80" ht="120" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>BUG-20260914-079</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>14:05:00</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Silent wrongness</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Alert, non-suppressible</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Drop everything -- blocks merge</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>PRS</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>The full order_lives re-fold ran automatically at writer startup and materialised every qualifying events row in memory before writing anything; on the Operator's real store (11M events, 3.7M lives, 14 GB) it made no measurable progress in ten minutes while holding the writer lock, so the dashboard served nothing</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>BUG-20260911-076 correctly made ORDER_LIVES_METHOD readable and triggered a full re-fold when a store predated the current rules. What it did not do was bound that work. _refresh_chunk materialises the whole result set into a Python dict keyed by order_hash before folding anything, which is fine for the incremental path (400 hashes at a time) and catastrophic for the full one. It was measured at 6.6s on 200k synthetic lives and shipped on that number; the tech-lead's review said in writing that this was not the number for the Operator's machine, and that caveat was not acted on.</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>None to the record. order_lives is DERIVED and the re-fold is one transaction, so the interrupted run committed nothing and every row stayed at its old method_version. The landing zone was never read. The cost was availability: the dashboard was unusable for the duration and had to be stopped by hand.</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>Nothing measured this against a store of the Operator's size before it shipped. Every gate ran against synthetic fixtures two orders of magnitude smaller. The standing correction: performance claims about the analytical store are not verified until they are verified on a copy of the real one.</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>REQ-N-16</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>src/navanax/normalize.py:L1230  ·  src/navanax/normalize.py:L1102</t>
+        </is>
+      </c>
+      <c r="T80" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/spencerwon/navanax1/blob/tester/src/navanax/normalize.py#L1230 https://github.com/spencerwon/navanax1/blob/tester/src/navanax/normalize.py#L1102</t>
+        </is>
+      </c>
+      <c r="U80" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py::test_order_lives_refolds_when_the_method_stamp_is_stale tests/selftest.py::test_order_lives_method_mixed_is_reported_on_health_as_warn</t>
+        </is>
+      </c>
+      <c r="V80" s="3" t="inlineStr">
+        <is>
+          <t>the Operator, on his own machine, immediately after the deploy</t>
+        </is>
+      </c>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="X80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T13:47:10-05:00</t>
+        </is>
+      </c>
+      <c r="Y80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T14:05:00-05:00</t>
+        </is>
+      </c>
+      <c r="Z80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T14:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="AA80" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11525,10 +11654,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA78" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T79" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA79" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T80" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId148"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId149"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11607,11 +11737,11 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A5,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A5,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$79,$A5)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$80,$A5)</f>
         <v/>
       </c>
     </row>
@@ -11632,11 +11762,11 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A6,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A6,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$79,$A6)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$80,$A6)</f>
         <v/>
       </c>
     </row>
@@ -11657,11 +11787,11 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A7,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A7,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$79,$A7)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$80,$A7)</f>
         <v/>
       </c>
     </row>
@@ -11682,11 +11812,11 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A8,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A8,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$79,$A8)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$80,$A8)</f>
         <v/>
       </c>
     </row>
@@ -11707,11 +11837,11 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A9,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A9,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$79,$A9)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$80,$A9)</f>
         <v/>
       </c>
     </row>
@@ -11732,11 +11862,11 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$79,$A10,'Bug log'!$K$2:$K$79,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A10,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$79,$A10)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$80,$A10)</f>
         <v/>
       </c>
     </row>

--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -273,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA80" headerRowCount="1">
-  <autoFilter ref="A1:AA80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA81" headerRowCount="1">
+  <autoFilter ref="A1:AA81"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA80"/>
+  <dimension ref="A1:AA81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11504,6 +11504,135 @@
         </is>
       </c>
       <c r="AA80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="120" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>BUG-20260914-080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>15:10:00</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Silent wrongness</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Alert, non-suppressible</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Drop everything -- blocks merge</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>PRS</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>Every page request took the fold's lock and the fold's connection, so a click waited behind the whole fold; and Health, status and the dedup block each ran full COUNT(*) scans over 11M events on every call (14.8s and 20.8s measured on the real store). Together they made the dashboard unresponsive at the Operator's scale</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>One sqlite3 connection, one threading.Lock, shared by the background fold and every API handler. Correct on a fixture where a fold takes milliseconds; on the real store a catch-up fold holds the lock for minutes and the page queues behind it. Separately, api_health counted seven tables with COUNT(*) on every call and api_status and api_dedup each scanned events in full -- roughly a minute of scanning per page load before a single chart was drawn.</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>None to the record. Availability only: the page could not answer while a fold ran, and after any downtime a fold runs for minutes.</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>No test ever ran a fold slow enough to notice the page waiting for it, and no measurement of a COUNT(*) was ever taken on the real store. The regression test below makes the fold artificially slow and asserts the page still answers.</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>REQ-N-16</t>
+        </is>
+      </c>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>src/navanax/dashboard.py:L96  ·  src/navanax/dashboard.py:L334  ·  src/navanax/dashboard.py:L937</t>
+        </is>
+      </c>
+      <c r="T81" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L96 https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L334 https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L937</t>
+        </is>
+      </c>
+      <c r="U81" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py::test_page_requests_do_not_wait_for_the_fold</t>
+        </is>
+      </c>
+      <c r="V81" s="3" t="inlineStr">
+        <is>
+          <t>the Operator, on his own machine: the page loaded and every number stayed at '...'</t>
+        </is>
+      </c>
+      <c r="W81" s="3" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="X81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T14:39:00-05:00</t>
+        </is>
+      </c>
+      <c r="Y81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:10:00-05:00</t>
+        </is>
+      </c>
+      <c r="Z81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:25:00-05:00</t>
+        </is>
+      </c>
+      <c r="AA81" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11655,10 +11784,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T79" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA79" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T80" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T81" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId149"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId150"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11737,11 +11867,11 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A5,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A5,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$80,$A5)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$81,$A5)</f>
         <v/>
       </c>
     </row>
@@ -11762,11 +11892,11 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A6,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A6,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$80,$A6)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$81,$A6)</f>
         <v/>
       </c>
     </row>
@@ -11787,11 +11917,11 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A7,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A7,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$80,$A7)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$81,$A7)</f>
         <v/>
       </c>
     </row>
@@ -11812,11 +11942,11 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A8,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A8,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$80,$A8)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$81,$A8)</f>
         <v/>
       </c>
     </row>
@@ -11837,11 +11967,11 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A9,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A9,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$80,$A9)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$81,$A9)</f>
         <v/>
       </c>
     </row>
@@ -11862,11 +11992,11 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$80,$A10,'Bug log'!$K$2:$K$80,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A10,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$80,$A10)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$81,$A10)</f>
         <v/>
       </c>
     </row>

--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -273,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA81" headerRowCount="1">
-  <autoFilter ref="A1:AA81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA82" headerRowCount="1">
+  <autoFilter ref="A1:AA82"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA81"/>
+  <dimension ref="A1:AA82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11633,6 +11633,135 @@
         </is>
       </c>
       <c r="AA81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="120" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>BUG-20260914-081</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>15:58:00</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Silent wrongness</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Alert, non-suppressible</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Drop everything -- blocks merge</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>PRS</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>Health ran PRAGMA quick_check -- which reads every page of the store -- on its first call and every ten minutes after, on the request path, holding the page's read lock; on the 14 GB real store that is minutes per run, so the page kept hanging after BUG-080's fix</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>A full-file read scheduled on the request path with a ten-minute TTL, sized for a store that no longer exists. quick_check(1) on 14 GB reads 14 GB.</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>None to the record; availability only. The comment beside the constant said "on the Operator's 2.8 GB store that is seconds" -- true when it was written, and the store is now five times that size.</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>The same gap as BUG-080: nothing measured this on the real store, and the constant's own comment recorded the size assumption without anything checking it. The regression test forces the large-store path and asserts the request returns in under a second.</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>REQ-N-16</t>
+        </is>
+      </c>
+      <c r="R82" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>src/navanax/dashboard.py:L59  ·  src/navanax/dashboard.py:L705</t>
+        </is>
+      </c>
+      <c r="T82" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L59 https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L705</t>
+        </is>
+      </c>
+      <c r="U82" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py::test_page_requests_do_not_wait_for_the_fold</t>
+        </is>
+      </c>
+      <c r="V82" s="3" t="inlineStr">
+        <is>
+          <t>the Operator's dashboard, redeployed with BUG-080's fix: /api/health still did not answer in 50s</t>
+        </is>
+      </c>
+      <c r="W82" s="3" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="X82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:55:00-05:00</t>
+        </is>
+      </c>
+      <c r="Y82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:58:00-05:00</t>
+        </is>
+      </c>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:05:00-05:00</t>
+        </is>
+      </c>
+      <c r="AA82" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11785,10 +11914,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA79" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T80" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T81" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T82" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId150"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId151"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11867,11 +11997,11 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A5,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A5,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$81,$A5)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$82,$A5)</f>
         <v/>
       </c>
     </row>
@@ -11892,11 +12022,11 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A6,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A6,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$81,$A6)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$82,$A6)</f>
         <v/>
       </c>
     </row>
@@ -11917,11 +12047,11 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A7,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A7,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$81,$A7)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$82,$A7)</f>
         <v/>
       </c>
     </row>
@@ -11942,11 +12072,11 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A8,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A8,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$81,$A8)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$82,$A8)</f>
         <v/>
       </c>
     </row>
@@ -11967,11 +12097,11 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A9,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A9,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$81,$A9)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$82,$A9)</f>
         <v/>
       </c>
     </row>
@@ -11992,11 +12122,11 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$81,$A10,'Bug log'!$K$2:$K$81,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A10,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$81,$A10)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$82,$A10)</f>
         <v/>
       </c>
     </row>

--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -273,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA82" headerRowCount="1">
-  <autoFilter ref="A1:AA82"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA83" headerRowCount="1">
+  <autoFilter ref="A1:AA83"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA82"/>
+  <dimension ref="A1:AA83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11762,6 +11762,135 @@
         </is>
       </c>
       <c r="AA82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="120" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>BUG-20260914-082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>16:32:00</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Data loss / availability</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Record the gap, never fill it</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Drop everything -- blocks merge</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>PRS</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>The background table counts introduced by BUG-080 ran on the page's own read connection under the page's own lock, so for the minute-plus they take on the real store -- and they start the moment the dashboard opens -- every page request queued behind them; the page was unresponsive for its first minutes and again every ten minutes</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>BUG-080's fix moved page reads off the writer's connection but put the new background counts on that same page connection, under the same lock. A sqlite3 connection serialises its statements, so a 21-second COUNT(*) on order_lives blocked every request sharing it, lock or no lock.</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>None to the record; availability only.</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>Same as BUG-080 and BUG-081: nothing timed a request on the real store before the fix shipped. The endpoint-by-endpoint timing that found this is now the acceptance test for the dashboard on the Operator's machine.</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>REQ-N-16</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>src/navanax/dashboard.py:L300</t>
+        </is>
+      </c>
+      <c r="T83" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L300</t>
+        </is>
+      </c>
+      <c r="U83" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py::test_page_requests_do_not_wait_for_the_fold</t>
+        </is>
+      </c>
+      <c r="V83" s="3" t="inlineStr">
+        <is>
+          <t>timing each endpoint from the page after the BUG-081 deploy: /api/meta answered in 0.0s, /api/status did not answer in eight minutes</t>
+        </is>
+      </c>
+      <c r="W83" s="3" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="X83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:22:00-05:00</t>
+        </is>
+      </c>
+      <c r="Y83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:32:00-05:00</t>
+        </is>
+      </c>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:40:00-05:00</t>
+        </is>
+      </c>
+      <c r="AA83" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11915,10 +12044,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T80" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T81" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T82" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T83" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId151"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId152"/>
   </tableParts>
 </worksheet>
 </file>
@@ -11997,11 +12127,11 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A5,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A5,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$82,$A5)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$83,$A5)</f>
         <v/>
       </c>
     </row>
@@ -12022,11 +12152,11 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A6,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A6,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$82,$A6)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$83,$A6)</f>
         <v/>
       </c>
     </row>
@@ -12047,11 +12177,11 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A7,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A7,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$82,$A7)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$83,$A7)</f>
         <v/>
       </c>
     </row>
@@ -12072,11 +12202,11 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A8,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A8,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$82,$A8)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$83,$A8)</f>
         <v/>
       </c>
     </row>
@@ -12097,11 +12227,11 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A9,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A9,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$82,$A9)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$83,$A9)</f>
         <v/>
       </c>
     </row>
@@ -12122,11 +12252,11 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$82,$A10,'Bug log'!$K$2:$K$82,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A10,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$82,$A10)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$83,$A10)</f>
         <v/>
       </c>
     </row>

--- a/docs/logs/BUGS.xlsx
+++ b/docs/logs/BUGS.xlsx
@@ -273,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA83" headerRowCount="1">
-  <autoFilter ref="A1:AA83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BugLog" displayName="BugLog" ref="A1:AA84" headerRowCount="1">
+  <autoFilter ref="A1:AA84"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Date"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA83"/>
+  <dimension ref="A1:AA84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11891,6 +11891,135 @@
         </is>
       </c>
       <c r="AA83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="120" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>BUG-20260914-083</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>17:40:00</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Silent wrongness</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Alert, non-suppressible</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Drop everything -- blocks merge</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>PRS</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>The main tab could not load on the real store: live_book scanned every placement event ever recorded for the collection with two subqueries per row (459.8 s measured), status ran two full-table scans on every call (26.2 s for the ETH/USD rate, 15.3 s for MAX(valid_ts)), and the page started a new refresh every 10 s regardless of whether the last one had returned, so requests piled up without bound</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>live_book took "the book" from events: every item_listed / item_received_bid / collection_offer row the collection ever produced, an EXISTS into order_lives per row to ask whether it still stands, a scalar subquery per row for quantity, then a sort of all of it for the top 25. order_lives IS the book -- one de-duplicated row per order with price, token, maker, expiry and termination -- and was never read for this. Status looked up the ETH/USD rate with ORDER BY valid_ts DESC LIMIT 1 over rows carrying a rate, which no index served, and took MAX(valid_ts) with no single-column index. The page's refresh timer had no notion of a refresh still in flight.</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>None to the record; availability only. Every chart series measured 0.0-1.7 s at every range, so the history and the USD view were always there -- the page never finished loading to show them.</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>The gap that produced BUG-080/081/082 as well, now closed by method rather than by patch: a consistent snapshot of the real store is taken with SQLite's online backup and every metric the page calls is timed against it natively before anything is called fixed. survival_prepare over 7 days measured 128.9 s and wallets over 24 h 19.2 s in the same run -- the Flow and Wallets tabs -- and are logged as the next items, not folded into this one.</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>REQ-N-16</t>
+        </is>
+      </c>
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>src/navanax/metrics.py:L2027  ·  src/navanax/dashboard.py:L440  ·  src/navanax/ui/index.html:L1204</t>
+        </is>
+      </c>
+      <c r="T84" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/spencerwon/navanax1/blob/tester/src/navanax/metrics.py#L2027 https://github.com/spencerwon/navanax1/blob/tester/src/navanax/dashboard.py#L440 https://github.com/spencerwon/navanax1/blob/tester/src/navanax/ui/index.html#L1204</t>
+        </is>
+      </c>
+      <c r="U84" s="6" t="inlineStr">
+        <is>
+          <t>tests/selftest.py::test_metric_engine_contract</t>
+        </is>
+      </c>
+      <c r="V84" s="3" t="inlineStr">
+        <is>
+          <t>timing every metric the page calls against a consistent snapshot of the Operator's 14.5 GB store, natively on his Mac (docs/04 s8.14)</t>
+        </is>
+      </c>
+      <c r="W84" s="3" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="X84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:30:00-05:00</t>
+        </is>
+      </c>
+      <c r="Y84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T17:40:00-05:00</t>
+        </is>
+      </c>
+      <c r="Z84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14T18:10:00-05:00</t>
+        </is>
+      </c>
+      <c r="AA84" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12045,10 +12174,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T81" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T82" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T83" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T84" r:id="rId152"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId152"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId153"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12127,11 +12257,11 @@
         </is>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A5,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$84,$A5,'Bug log'!$K$2:$K$84,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$83,$A5)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$84,$A5)</f>
         <v/>
       </c>
     </row>
@@ -12152,11 +12282,11 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A6,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$84,$A6,'Bug log'!$K$2:$K$84,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$83,$A6)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$84,$A6)</f>
         <v/>
       </c>
     </row>
@@ -12177,11 +12307,11 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A7,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$84,$A7,'Bug log'!$K$2:$K$84,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$83,$A7)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$84,$A7)</f>
         <v/>
       </c>
     </row>
@@ -12202,11 +12332,11 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A8,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$84,$A8,'Bug log'!$K$2:$K$84,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$83,$A8)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$84,$A8)</f>
         <v/>
       </c>
     </row>
@@ -12227,11 +12357,11 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A9,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$84,$A9,'Bug log'!$K$2:$K$84,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$83,$A9)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$84,$A9)</f>
         <v/>
       </c>
     </row>
@@ -12252,11 +12382,11 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('Bug log'!$D$2:$D$83,$A10,'Bug log'!$K$2:$K$83,"&lt;&gt;fixed")</f>
+        <f>COUNTIFS('Bug log'!$D$2:$D$84,$A10,'Bug log'!$K$2:$K$84,"&lt;&gt;fixed")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF('Bug log'!$D$2:$D$83,$A10)</f>
+        <f>COUNTIF('Bug log'!$D$2:$D$84,$A10)</f>
         <v/>
       </c>
     </row>
